--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -544,7 +544,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0008125834349062627</v>
+        <v>0.0008439836026042923</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +600,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01329154332810958</v>
+        <v>0.01374487581384133</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.07069475883684485</v>
+        <v>0.07318543525440077</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.05078646468164142</v>
+        <v>0.05184470701712081</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14893</v>
+        <v>14272</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8644146497184979</v>
+        <v>0.8603809983120327</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>13454</v>
+        <v>12890</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7808926809449185</v>
+        <v>0.7770677598263805</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1137</v>
+        <v>1089</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.06599338324917291</v>
+        <v>0.0656498673740053</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +789,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1218</v>
+        <v>1196</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07069475883684485</v>
+        <v>0.07210031347962383</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1420</v>
+        <v>1413</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.08241917696906378</v>
+        <v>0.08518205931999036</v>
       </c>
     </row>
   </sheetData>
@@ -858,7 +858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7864,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 15:08 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -23,12 +23,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
-    <numFmt numFmtId="166" formatCode="$0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +54,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A8377"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -134,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,11 +152,10 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -585,7 +588,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0.0008439836026042923</v>
+        <v>0.0008125834349062627</v>
       </c>
     </row>
     <row r="7">
@@ -600,10 +603,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.01374487581384133</v>
+        <v>0.01329154332810958</v>
       </c>
     </row>
     <row r="8">
@@ -618,10 +621,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.07318543525440077</v>
+        <v>0.07069475883684485</v>
       </c>
     </row>
     <row r="9">
@@ -636,10 +639,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.05184470701712081</v>
+        <v>0.05078646468164142</v>
       </c>
     </row>
     <row r="10">
@@ -654,10 +657,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>14272</v>
+        <v>14893</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.8603809983120327</v>
+        <v>0.8644146497184979</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -753,10 +756,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>12890</v>
+        <v>13454</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.7770677598263805</v>
+        <v>0.7808926809449185</v>
       </c>
     </row>
     <row r="8">
@@ -771,10 +774,10 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1089</v>
+        <v>1137</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.0656498673740053</v>
+        <v>0.06599338324917291</v>
       </c>
     </row>
     <row r="9">
@@ -789,10 +792,10 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1196</v>
+        <v>1218</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.07210031347962383</v>
+        <v>0.07069475883684485</v>
       </c>
     </row>
     <row r="10">
@@ -807,10 +810,10 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0.08518205931999036</v>
+        <v>0.08241917696906378</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +841,7 @@
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -858,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -910,7 +913,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -920,7 +923,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -960,10 +963,10 @@
       <c r="I6" s="14" t="n">
         <v>0.005662596549089983</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="13" t="n">
         <v>82.18673203940752</v>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1010,10 +1013,10 @@
       <c r="I7" s="14" t="n">
         <v>0.007516813272747278</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="13" t="n">
         <v>149.5518557714214</v>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1060,10 +1063,10 @@
       <c r="I8" s="14" t="n">
         <v>0.07763545608087986</v>
       </c>
-      <c r="J8" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="J8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1110,10 +1113,10 @@
       <c r="I9" s="14" t="n">
         <v>0.001765023156357218</v>
       </c>
-      <c r="J9" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1160,10 +1163,10 @@
       <c r="I10" s="14" t="n">
         <v>0.006949900313073</v>
       </c>
-      <c r="J10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="J10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1210,10 +1213,10 @@
       <c r="I11" s="14" t="n">
         <v>0.005147712757825382</v>
       </c>
-      <c r="J11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="J11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1260,10 +1263,10 @@
       <c r="I12" s="14" t="n">
         <v>0.07336967551747021</v>
       </c>
-      <c r="J12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="J12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1310,10 +1313,10 @@
       <c r="I13" s="14" t="n">
         <v>0.004500315753696198</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="13" t="n">
         <v>146.6743235597305</v>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1360,10 +1363,10 @@
       <c r="I14" s="14" t="n">
         <v>0.01116536253527052</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="13" t="n">
         <v>452.4792782741477</v>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1410,10 +1413,10 @@
       <c r="I15" s="14" t="n">
         <v>0.06449401889003488</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="13" t="n">
         <v>216.4873320545357</v>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -1460,10 +1463,10 @@
       <c r="I16" s="14" t="n">
         <v>0.01160563931069558</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="13" t="n">
         <v>137.7312623785126</v>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1510,10 +1513,10 @@
       <c r="I17" s="14" t="n">
         <v>0.01001435062238145</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="13" t="n">
         <v>51.94697222468491</v>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1560,10 +1563,10 @@
       <c r="I18" s="14" t="n">
         <v>0.01339589643659371</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="13" t="n">
         <v>336.7856445325167</v>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1610,10 +1613,10 @@
       <c r="I19" s="14" t="n">
         <v>0.01197681130476525</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="13" t="n">
         <v>122.9867536455535</v>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1660,10 +1663,10 @@
       <c r="I20" s="14" t="n">
         <v>0.026139962613445</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="13" t="n">
         <v>570.1296508763407</v>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1710,10 +1713,10 @@
       <c r="I21" s="14" t="n">
         <v>0.0129222031183726</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="13" t="n">
         <v>371.2167917333029</v>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1760,10 +1763,10 @@
       <c r="I22" s="14" t="n">
         <v>0.0111865339714305</v>
       </c>
-      <c r="J22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="J22" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1810,10 +1813,10 @@
       <c r="I23" s="14" t="n">
         <v>0.005786839661133043</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="13" t="n">
         <v>69.95266758973155</v>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1860,10 +1863,10 @@
       <c r="I24" s="14" t="n">
         <v>0.006869583641978683</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="13" t="n">
         <v>524.5716731254472</v>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1910,10 +1913,10 @@
       <c r="I25" s="14" t="n">
         <v>0.01037521531710376</v>
       </c>
-      <c r="J25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="J25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -1960,10 +1963,10 @@
       <c r="I26" s="14" t="n">
         <v>0.0006901335122952734</v>
       </c>
-      <c r="J26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="J26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2010,10 +2013,10 @@
       <c r="I27" s="14" t="n">
         <v>0.01670782296794169</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="13" t="n">
         <v>262.4649081206016</v>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2060,10 +2063,10 @@
       <c r="I28" s="14" t="n">
         <v>0.004304424713229357</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="13" t="n">
         <v>349.636710168589</v>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2110,10 +2113,10 @@
       <c r="I29" s="14" t="n">
         <v>0.0124318617006991</v>
       </c>
-      <c r="J29" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="J29" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2160,10 +2163,10 @@
       <c r="I30" s="14" t="n">
         <v>0.007083788262992614</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="13" t="n">
         <v>544.7197336927721</v>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2210,10 +2213,10 @@
       <c r="I31" s="14" t="n">
         <v>0.00049584600885172</v>
       </c>
-      <c r="J31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="J31" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2260,10 +2263,10 @@
       <c r="I32" s="14" t="n">
         <v>0.04647613709178894</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="13" t="n">
         <v>154.2943741827868</v>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2310,10 +2313,10 @@
       <c r="I33" s="14" t="n">
         <v>0.009430290636670972</v>
       </c>
-      <c r="J33" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="J33" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2360,10 +2363,10 @@
       <c r="I34" s="14" t="n">
         <v>0.02082125104408483</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="13" t="n">
         <v>48.93750147321273</v>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2410,10 +2413,10 @@
       <c r="I35" s="14" t="n">
         <v>0.0412037248697904</v>
       </c>
-      <c r="J35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="J35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2460,10 +2463,10 @@
       <c r="I36" s="14" t="n">
         <v>0.01158609525139104</v>
       </c>
-      <c r="J36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="J36" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2510,10 +2513,10 @@
       <c r="I37" s="14" t="n">
         <v>0.006976809481722381</v>
       </c>
-      <c r="J37" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="J37" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2560,10 +2563,10 @@
       <c r="I38" s="14" t="n">
         <v>0.0009488901706141738</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="13" t="n">
         <v>412.6862773857025</v>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2610,10 +2613,10 @@
       <c r="I39" s="14" t="n">
         <v>0.01733663874266193</v>
       </c>
-      <c r="J39" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="J39" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2660,10 +2663,10 @@
       <c r="I40" s="14" t="n">
         <v>0.003301513721226442</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="13" t="n">
         <v>260.9417532318429</v>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2710,10 +2713,10 @@
       <c r="I41" s="14" t="n">
         <v>0.02313322519215015</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="13" t="n">
         <v>507.5651456724117</v>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2760,10 +2763,10 @@
       <c r="I42" s="14" t="n">
         <v>0.01899649232750165</v>
       </c>
-      <c r="J42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="J42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2810,10 +2813,10 @@
       <c r="I43" s="14" t="n">
         <v>0.01992207890418162</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="13" t="n">
         <v>200.5911203041729</v>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2860,10 +2863,10 @@
       <c r="I44" s="14" t="n">
         <v>0.04982688311124306</v>
       </c>
-      <c r="J44" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="J44" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -2910,10 +2913,10 @@
       <c r="I45" s="14" t="n">
         <v>0.0100231031452753</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="13" t="n">
         <v>372.7994584318193</v>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -2960,10 +2963,10 @@
       <c r="I46" s="14" t="n">
         <v>0.02010649783161631</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="13" t="n">
         <v>475.2799031742837</v>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3010,10 +3013,10 @@
       <c r="I47" s="14" t="n">
         <v>0.006578102679172628</v>
       </c>
-      <c r="J47" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="J47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3060,10 +3063,10 @@
       <c r="I48" s="14" t="n">
         <v>0.01958779342574608</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="13" t="n">
         <v>76.86399332428276</v>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3110,10 +3113,10 @@
       <c r="I49" s="14" t="n">
         <v>0.01480533684619233</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="13" t="n">
         <v>538.8677426030803</v>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3160,10 +3163,10 @@
       <c r="I50" s="14" t="n">
         <v>0.03014752515286178</v>
       </c>
-      <c r="J50" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="J50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -3210,10 +3213,10 @@
       <c r="I51" s="14" t="n">
         <v>0.01174854910995379</v>
       </c>
-      <c r="J51" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
+      <c r="J51" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3260,10 +3263,10 @@
       <c r="I52" s="14" t="n">
         <v>0.01138047607739067</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="13" t="n">
         <v>227.7921981587305</v>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3310,10 +3313,10 @@
       <c r="I53" s="14" t="n">
         <v>0.0160985614331324</v>
       </c>
-      <c r="J53" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="J53" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3360,10 +3363,10 @@
       <c r="I54" s="14" t="n">
         <v>0.03006584180849616</v>
       </c>
-      <c r="J54" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="J54" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -3410,10 +3413,10 @@
       <c r="I55" s="14" t="n">
         <v>0.02694674668525057</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="13" t="n">
         <v>62.38652974331646</v>
       </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -3466,7 +3469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5566,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -5608,7 +5611,7 @@
       <c r="I6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="13" t="n">
         <v>1090.082147150696</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -5653,7 +5656,7 @@
       <c r="I7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -5698,7 +5701,7 @@
       <c r="I8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -5743,7 +5746,7 @@
       <c r="I9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -5788,7 +5791,7 @@
       <c r="I10" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -5833,7 +5836,7 @@
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -5878,7 +5881,7 @@
       <c r="I12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -5923,7 +5926,7 @@
       <c r="I13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -5968,7 +5971,7 @@
       <c r="I14" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J14" s="15" t="n">
+      <c r="J14" s="13" t="n">
         <v>2827.783123696932</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -6013,7 +6016,7 @@
       <c r="I15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="15" t="n">
+      <c r="J15" s="13" t="n">
         <v>701.3880969299285</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -6058,7 +6061,7 @@
       <c r="I16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="15" t="n">
+      <c r="J16" s="13" t="n">
         <v>2382.137093831345</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -6103,7 +6106,7 @@
       <c r="I17" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J17" s="15" t="n">
+      <c r="J17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="8" t="inlineStr">
@@ -6148,7 +6151,7 @@
       <c r="I18" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J18" s="15" t="n">
+      <c r="J18" s="13" t="n">
         <v>2429.077649324834</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -6193,7 +6196,7 @@
       <c r="I19" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="J19" s="15" t="n">
+      <c r="J19" s="13" t="n">
         <v>3395.305835435769</v>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -6238,7 +6241,7 @@
       <c r="I20" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="15" t="n">
+      <c r="J20" s="13" t="n">
         <v>8106.128850713634</v>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -6283,7 +6286,7 @@
       <c r="I21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J21" s="15" t="n">
+      <c r="J21" s="13" t="n">
         <v>876.8078127967395</v>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -6328,7 +6331,7 @@
       <c r="I22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="15" t="n">
+      <c r="J22" s="13" t="n">
         <v>5103.936072566275</v>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -6373,7 +6376,7 @@
       <c r="I23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="J23" s="15" t="n">
+      <c r="J23" s="13" t="n">
         <v>216.4873320545357</v>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -6418,7 +6421,7 @@
       <c r="I24" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="15" t="n">
+      <c r="J24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -6463,7 +6466,7 @@
       <c r="I25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="15" t="n">
+      <c r="J25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -6508,7 +6511,7 @@
       <c r="I26" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="J26" s="15" t="n">
+      <c r="J26" s="13" t="n">
         <v>2266.94199288456</v>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -6553,7 +6556,7 @@
       <c r="I27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="15" t="n">
+      <c r="J27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -6598,7 +6601,7 @@
       <c r="I28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="15" t="n">
+      <c r="J28" s="13" t="n">
         <v>309.4502762224989</v>
       </c>
       <c r="K28" s="8" t="inlineStr">
@@ -6643,7 +6646,7 @@
       <c r="I29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="15" t="n">
+      <c r="J29" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -6688,7 +6691,7 @@
       <c r="I30" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="15" t="n">
+      <c r="J30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -6733,7 +6736,7 @@
       <c r="I31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="15" t="n">
+      <c r="J31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -6778,7 +6781,7 @@
       <c r="I32" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="15" t="n">
+      <c r="J32" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -6823,7 +6826,7 @@
       <c r="I33" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="J33" s="15" t="n">
+      <c r="J33" s="13" t="n">
         <v>2178.424359012894</v>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -6868,7 +6871,7 @@
       <c r="I34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J34" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -6913,7 +6916,7 @@
       <c r="I35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="15" t="n">
+      <c r="J35" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -6958,7 +6961,7 @@
       <c r="I36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="15" t="n">
+      <c r="J36" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -7003,7 +7006,7 @@
       <c r="I37" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J37" s="15" t="n">
+      <c r="J37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -7048,7 +7051,7 @@
       <c r="I38" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J38" s="15" t="n">
+      <c r="J38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -7093,7 +7096,7 @@
       <c r="I39" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J39" s="15" t="n">
+      <c r="J39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -7138,7 +7141,7 @@
       <c r="I40" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="15" t="n">
+      <c r="J40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -7183,7 +7186,7 @@
       <c r="I41" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="15" t="n">
+      <c r="J41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="7" t="inlineStr">
@@ -7228,7 +7231,7 @@
       <c r="I42" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="15" t="n">
+      <c r="J42" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="8" t="inlineStr">
@@ -7273,7 +7276,7 @@
       <c r="I43" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="15" t="n">
+      <c r="J43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -7318,7 +7321,7 @@
       <c r="I44" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="15" t="n">
+      <c r="J44" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -7363,7 +7366,7 @@
       <c r="I45" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J45" s="15" t="n">
+      <c r="J45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -7408,7 +7411,7 @@
       <c r="I46" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="15" t="n">
+      <c r="J46" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -7453,7 +7456,7 @@
       <c r="I47" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="J47" s="15" t="n">
+      <c r="J47" s="13" t="n">
         <v>978.1772207563768</v>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -7498,7 +7501,7 @@
       <c r="I48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="15" t="n">
+      <c r="J48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="7" t="inlineStr">
@@ -7543,7 +7546,7 @@
       <c r="I49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="15" t="n">
+      <c r="J49" s="13" t="n">
         <v>282.1137928542947</v>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -7588,7 +7591,7 @@
       <c r="I50" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="15" t="n">
+      <c r="J50" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="7" t="inlineStr">
@@ -7633,7 +7636,7 @@
       <c r="I51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="15" t="n">
+      <c r="J51" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -7678,7 +7681,7 @@
       <c r="I52" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="15" t="n">
+      <c r="J52" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -7723,7 +7726,7 @@
       <c r="I53" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="15" t="n">
+      <c r="J53" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -7768,7 +7771,7 @@
       <c r="I54" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J54" s="15" t="n">
+      <c r="J54" s="13" t="n">
         <v>497.3645606304697</v>
       </c>
       <c r="K54" s="8" t="inlineStr">
@@ -7813,7 +7816,7 @@
       <c r="I55" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="15" t="n">
+      <c r="J55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -7864,7 +7867,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7901,7 +7904,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -7911,7 +7914,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7939,7 @@
       <c r="F6" s="14" t="n">
         <v>0.0096918935358258</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>360.5778351845597</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -7944,7 +7947,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7971,7 +7974,7 @@
       <c r="F7" s="14" t="n">
         <v>0.01006917342062136</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>945.7779688953165</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -7979,7 +7982,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8006,7 +8009,7 @@
       <c r="F8" s="14" t="n">
         <v>0.03962907977798009</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>405.138896801978</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -8014,7 +8017,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8041,7 +8044,7 @@
       <c r="F9" s="14" t="n">
         <v>0.006014900700062473</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>57.6271390555138</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -8049,7 +8052,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8076,7 +8079,7 @@
       <c r="F10" s="14" t="n">
         <v>0.01322551928021331</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>1129.81241493739</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -8084,7 +8087,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8111,7 +8114,7 @@
       <c r="F11" s="14" t="n">
         <v>0.00870108695044702</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>29.33688303623523</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -8119,7 +8122,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8146,7 +8149,7 @@
       <c r="F12" s="14" t="n">
         <v>0.04955166949076883</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>161.0086447691849</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -8154,7 +8157,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8181,7 +8184,7 @@
       <c r="F13" s="14" t="n">
         <v>0.01783846325906168</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>48.88801358972812</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -8189,7 +8192,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8216,7 +8219,7 @@
       <c r="F14" s="14" t="n">
         <v>0.07713775226424831</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>115.0555744091059</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -8224,7 +8227,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8251,7 +8254,7 @@
       <c r="F15" s="14" t="n">
         <v>0.01489800694594049</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -8259,7 +8262,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8286,7 +8289,7 @@
       <c r="F16" s="14" t="n">
         <v>0.02086350081712876</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>191.9822585983175</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -8294,7 +8297,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8321,7 +8324,7 @@
       <c r="F17" s="14" t="n">
         <v>0.02836799948420991</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>577.464158867459</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
@@ -8329,7 +8332,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8356,7 +8359,7 @@
       <c r="F18" s="14" t="n">
         <v>0.01292028304314332</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>470.4541925498533</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -8364,7 +8367,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8391,7 +8394,7 @@
       <c r="F19" s="14" t="n">
         <v>0.1492904033285511</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>417.7377120305643</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -8399,7 +8402,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8426,7 +8429,7 @@
       <c r="F20" s="14" t="n">
         <v>0.02108151299180324</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>1404.102929621539</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -8434,7 +8437,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8461,7 +8464,7 @@
       <c r="F21" s="14" t="n">
         <v>0.02966766295883669</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>904.3755528014095</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -8469,7 +8472,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8496,7 +8499,7 @@
       <c r="F22" s="14" t="n">
         <v>0.01986596939873672</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>760.7946040789409</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -8504,7 +8507,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8531,7 +8534,7 @@
       <c r="F23" s="14" t="n">
         <v>0.004757047657066884</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>73.11400323032365</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -8539,7 +8542,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8566,7 +8569,7 @@
       <c r="F24" s="14" t="n">
         <v>0.04609730976437435</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -8574,7 +8577,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8601,7 +8604,7 @@
       <c r="F25" s="14" t="n">
         <v>0.03277068089712413</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>3431.642417621469</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
@@ -8609,7 +8612,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8636,7 +8639,7 @@
       <c r="F26" s="14" t="n">
         <v>0.04201769701905907</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>2806.005989108901</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -8644,7 +8647,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8671,7 +8674,7 @@
       <c r="F27" s="14" t="n">
         <v>0.02766562736064482</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>526.6306283078505</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -8679,7 +8682,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8706,7 +8709,7 @@
       <c r="F28" s="14" t="n">
         <v>0.02335462510910171</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>1937.475296851815</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -8714,7 +8717,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8741,7 +8744,7 @@
       <c r="F29" s="14" t="n">
         <v>0.00667195432752743</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>1318.48492887275</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -8749,7 +8752,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8776,7 +8779,7 @@
       <c r="F30" s="14" t="n">
         <v>0.01240040984368762</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>216.555202389515</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -8784,7 +8787,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -8811,7 +8814,7 @@
       <c r="F31" s="14" t="n">
         <v>0.1013218864814724</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -8819,7 +8822,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8846,7 +8849,7 @@
       <c r="F32" s="14" t="n">
         <v>0.01639094212672771</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>704.5927289461574</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -8854,7 +8857,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -8881,7 +8884,7 @@
       <c r="F33" s="14" t="n">
         <v>0.01365581293831585</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -8889,7 +8892,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -8916,7 +8919,7 @@
       <c r="F34" s="14" t="n">
         <v>0.01516184161165969</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>11266.35995908754</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -8924,7 +8927,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8951,7 +8954,7 @@
       <c r="F35" s="14" t="n">
         <v>0.036850284563122</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>2453.351275943414</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -8959,7 +8962,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8986,7 +8989,7 @@
       <c r="F36" s="14" t="n">
         <v>0.06554491320246605</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -8994,7 +8997,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9021,7 +9024,7 @@
       <c r="F37" s="14" t="n">
         <v>0.02357084771396693</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -9029,7 +9032,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9056,7 +9059,7 @@
       <c r="F38" s="14" t="n">
         <v>0.1024269966398655</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -9064,7 +9067,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9091,7 +9094,7 @@
       <c r="F39" s="14" t="n">
         <v>0.01365709021103395</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>2272.957289261953</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -9099,7 +9102,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9126,7 +9129,7 @@
       <c r="F40" s="14" t="n">
         <v>0.007753030622445371</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>687.6937397736509</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -9134,7 +9137,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9161,7 +9164,7 @@
       <c r="F41" s="14" t="n">
         <v>0.005098348428008417</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -9169,7 +9172,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9196,7 +9199,7 @@
       <c r="F42" s="14" t="n">
         <v>0.01978678673919397</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>506.1075925785744</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -9204,7 +9207,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9231,7 +9234,7 @@
       <c r="F43" s="14" t="n">
         <v>0.006030457952383283</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>79.60350298737045</v>
       </c>
       <c r="H43" s="10" t="inlineStr">
@@ -9239,7 +9242,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9266,7 +9269,7 @@
       <c r="F44" s="14" t="n">
         <v>0.05311269111638953</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>482.6559972125926</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -9274,7 +9277,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9301,7 +9304,7 @@
       <c r="F45" s="14" t="n">
         <v>0.006266721357941334</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -9309,7 +9312,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9336,7 +9339,7 @@
       <c r="F46" s="14" t="n">
         <v>0.01612926589949264</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>276.1740744376132</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -9344,7 +9347,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9371,7 +9374,7 @@
       <c r="F47" s="14" t="n">
         <v>0.1429302806565467</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>5867.815343286523</v>
       </c>
       <c r="H47" s="8" t="inlineStr">
@@ -9379,7 +9382,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -9406,7 +9409,7 @@
       <c r="F48" s="14" t="n">
         <v>0.01710252125617445</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>76.03827725395467</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -9414,7 +9417,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9441,7 +9444,7 @@
       <c r="F49" s="14" t="n">
         <v>0.009112253521380551</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>215.6704813078976</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -9449,7 +9452,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9476,7 +9479,7 @@
       <c r="F50" s="14" t="n">
         <v>0.00754717688951041</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>199.2808488528744</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -9484,7 +9487,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9511,7 +9514,7 @@
       <c r="F51" s="14" t="n">
         <v>0.03260189059669518</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>563.8826975406507</v>
       </c>
       <c r="H51" s="9" t="inlineStr">
@@ -9519,7 +9522,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9546,7 +9549,7 @@
       <c r="F52" s="14" t="n">
         <v>0.005580514301462096</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>267.3562685283252</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -9554,7 +9557,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9581,7 +9584,7 @@
       <c r="F53" s="14" t="n">
         <v>0.002990103740015137</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>215.1459643173814</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -9589,7 +9592,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9616,7 +9619,7 @@
       <c r="F54" s="14" t="n">
         <v>0.01164799757881128</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>107.7390975682393</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -9624,7 +9627,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9651,7 +9654,7 @@
       <c r="F55" s="14" t="n">
         <v>0.01934881456390502</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -9659,7 +9662,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9707,7 +9710,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9747,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -9754,7 +9757,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9782,7 @@
       <c r="F6" s="14" t="n">
         <v>0.02482260748073242</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>438.3880455199487</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -9787,7 +9790,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9814,7 +9817,7 @@
       <c r="F7" s="14" t="n">
         <v>0.0233089026103805</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>295.9942723681995</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -9822,7 +9825,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9849,7 +9852,7 @@
       <c r="F8" s="14" t="n">
         <v>0.0273809883977544</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>667.8119094642874</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -9857,7 +9860,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9884,7 +9887,7 @@
       <c r="F9" s="14" t="n">
         <v>0.02486781537412907</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>123.5713416743224</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -9892,7 +9895,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -9919,7 +9922,7 @@
       <c r="F10" s="14" t="n">
         <v>0.02346010631464422</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>492.1893653914581</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -9927,7 +9930,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -9954,7 +9957,7 @@
       <c r="F11" s="14" t="n">
         <v>0.01867311871043304</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>791.8916867894595</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
@@ -9962,7 +9965,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -9989,7 +9992,7 @@
       <c r="F12" s="14" t="n">
         <v>0.02531795900427907</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>291.8803778994528</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -9997,7 +10000,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10024,7 +10027,7 @@
       <c r="F13" s="14" t="n">
         <v>0.01243357678876132</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>279.5160802465603</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -10032,7 +10035,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10059,7 +10062,7 @@
       <c r="F14" s="14" t="n">
         <v>0.03226410986005102</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>356.5412904738232</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -10067,7 +10070,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10094,7 +10097,7 @@
       <c r="F15" s="14" t="n">
         <v>0.008844857451023981</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>471.9575974953452</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
@@ -10102,7 +10105,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10129,7 +10132,7 @@
       <c r="F16" s="14" t="n">
         <v>0.06078815239738682</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>250.7607034446635</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -10137,7 +10140,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10164,7 +10167,7 @@
       <c r="F17" s="14" t="n">
         <v>0.04067179033536839</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>465.6383535741126</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
@@ -10172,7 +10175,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10199,7 +10202,7 @@
       <c r="F18" s="14" t="n">
         <v>0.01064154278629253</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>562.4894764508234</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -10207,7 +10210,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10234,7 +10237,7 @@
       <c r="F19" s="14" t="n">
         <v>0.005752799409621038</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>396.6762473304616</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
@@ -10242,7 +10245,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10269,7 +10272,7 @@
       <c r="F20" s="14" t="n">
         <v>0.0237824209052562</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>887.5336049802796</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -10277,7 +10280,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10304,7 +10307,7 @@
       <c r="F21" s="14" t="n">
         <v>0.03972997325938393</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>983.6382995320548</v>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -10312,7 +10315,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10339,7 +10342,7 @@
       <c r="F22" s="14" t="n">
         <v>0.01050266197937607</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>775.5307629956412</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
@@ -10347,7 +10350,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10374,7 +10377,7 @@
       <c r="F23" s="14" t="n">
         <v>0.009362334211779533</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>378.5058578985251</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
@@ -10382,7 +10385,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10409,7 +10412,7 @@
       <c r="F24" s="14" t="n">
         <v>0.008267136722330485</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>257.7020402396228</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -10417,7 +10420,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10444,7 +10447,7 @@
       <c r="F25" s="14" t="n">
         <v>0.008543026617339413</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>731.3746833673922</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -10452,7 +10455,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10479,7 +10482,7 @@
       <c r="F26" s="14" t="n">
         <v>0.01071757900240779</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>949.7590844603892</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -10487,7 +10490,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10514,7 +10517,7 @@
       <c r="F27" s="14" t="n">
         <v>0.005876707397305275</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>434.5894638052597</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -10522,7 +10525,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10549,7 +10552,7 @@
       <c r="F28" s="14" t="n">
         <v>0.01057732256263786</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>399.8695733844439</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -10557,7 +10560,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10584,7 +10587,7 @@
       <c r="F29" s="14" t="n">
         <v>0.01139312626654418</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>292.9129380781301</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -10592,7 +10595,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10619,7 +10622,7 @@
       <c r="F30" s="14" t="n">
         <v>0.02768533998381936</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>1050.787662195776</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -10627,7 +10630,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10654,7 +10657,7 @@
       <c r="F31" s="14" t="n">
         <v>0.006123344660820004</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>385.8556610336719</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
@@ -10662,7 +10665,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10689,7 +10692,7 @@
       <c r="F32" s="14" t="n">
         <v>0.01563915113599137</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>88.94017771311448</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
@@ -10697,7 +10700,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -10724,7 +10727,7 @@
       <c r="F33" s="14" t="n">
         <v>0.02197167385022951</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>551.3121030342503</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
@@ -10732,7 +10735,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10759,7 +10762,7 @@
       <c r="F34" s="14" t="n">
         <v>0.01741993388136211</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>509.4619096695077</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
@@ -10767,7 +10770,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10794,7 +10797,7 @@
       <c r="F35" s="14" t="n">
         <v>0.008026271914698211</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>884.3172598553024</v>
       </c>
       <c r="H35" s="10" t="inlineStr">
@@ -10802,7 +10805,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10829,7 +10832,7 @@
       <c r="F36" s="14" t="n">
         <v>0.01041873426836739</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>543.1703210130681</v>
       </c>
       <c r="H36" s="10" t="inlineStr">
@@ -10837,7 +10840,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10864,7 +10867,7 @@
       <c r="F37" s="14" t="n">
         <v>0.01567417599310884</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>815.7106453891088</v>
       </c>
       <c r="H37" s="10" t="inlineStr">
@@ -10872,7 +10875,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10899,7 +10902,7 @@
       <c r="F38" s="14" t="n">
         <v>0.01112811003958464</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>738.5443422422857</v>
       </c>
       <c r="H38" s="10" t="inlineStr">
@@ -10907,7 +10910,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -10934,7 +10937,7 @@
       <c r="F39" s="14" t="n">
         <v>0.04502463473307715</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>212.8991281034186</v>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -10942,7 +10945,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -10969,7 +10972,7 @@
       <c r="F40" s="14" t="n">
         <v>0.008645980109005469</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>272.3920625371475</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -10977,7 +10980,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11004,7 +11007,7 @@
       <c r="F41" s="14" t="n">
         <v>0.003122234064568531</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>309.9367648933697</v>
       </c>
       <c r="H41" s="10" t="inlineStr">
@@ -11012,7 +11015,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11039,7 +11042,7 @@
       <c r="F42" s="14" t="n">
         <v>0.02857838926920902</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>3636.248539347248</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -11047,7 +11050,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -11074,7 +11077,7 @@
       <c r="F43" s="14" t="n">
         <v>0.0827454716023179</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>607.012830132915</v>
       </c>
       <c r="H43" s="8" t="inlineStr">
@@ -11082,7 +11085,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11109,7 +11112,7 @@
       <c r="F44" s="14" t="n">
         <v>0.1136296541084457</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>232.2417314539676</v>
       </c>
       <c r="H44" s="8" t="inlineStr">
@@ -11117,7 +11120,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11144,7 +11147,7 @@
       <c r="F45" s="14" t="n">
         <v>0.007227648553649886</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>281.7481280881721</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -11152,7 +11155,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11179,7 +11182,7 @@
       <c r="F46" s="14" t="n">
         <v>0.005056081284422543</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>493.0724164114965</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -11187,7 +11190,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11214,7 +11217,7 @@
       <c r="F47" s="14" t="n">
         <v>0.03519356969113496</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>417.1660550757397</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -11222,7 +11225,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11249,7 +11252,7 @@
       <c r="F48" s="14" t="n">
         <v>0.02722123084993133</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>572.5253890525843</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
@@ -11257,7 +11260,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11284,7 +11287,7 @@
       <c r="F49" s="14" t="n">
         <v>0.01313232170738979</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>340.9369159592807</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -11292,7 +11295,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11319,7 +11322,7 @@
       <c r="F50" s="14" t="n">
         <v>0.02934942734038223</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>647.1283529666207</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
@@ -11327,7 +11330,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11354,7 +11357,7 @@
       <c r="F51" s="14" t="n">
         <v>0.01085954363670688</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>1075.805153376018</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -11362,7 +11365,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11389,7 +11392,7 @@
       <c r="F52" s="14" t="n">
         <v>0.004271523786062976</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>404.6035441388313</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -11397,7 +11400,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11424,7 +11427,7 @@
       <c r="F53" s="14" t="n">
         <v>0.00340468035318777</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>421.6539659371526</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
@@ -11432,7 +11435,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11459,7 +11462,7 @@
       <c r="F54" s="14" t="n">
         <v>0.003708344283212438</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>482.8619129222179</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -11467,7 +11470,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11494,7 +11497,7 @@
       <c r="F55" s="14" t="n">
         <v>0.01294141056303134</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>655.9693756397734</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -11502,7 +11505,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11550,7 +11553,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:06 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11587,7 +11590,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>RPM</t>
+          <t>IPM (USD/M)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -11597,7 +11600,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>BandaRPM</t>
+          <t>Banda IPM</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11625,7 @@
       <c r="F6" s="14" t="n">
         <v>0.01029602817139427</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="13" t="n">
         <v>446.8410606127571</v>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -11630,7 +11633,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11657,7 +11660,7 @@
       <c r="F7" s="14" t="n">
         <v>0.02730424353286995</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="13" t="n">
         <v>700.2531949734986</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
@@ -11665,7 +11668,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11692,7 +11695,7 @@
       <c r="F8" s="14" t="n">
         <v>0.01447592790445943</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="13" t="n">
         <v>747.5947773574849</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
@@ -11700,7 +11703,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11727,7 +11730,7 @@
       <c r="F9" s="14" t="n">
         <v>0.01078246832737492</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="13" t="n">
         <v>492.1355981028595</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
@@ -11735,7 +11738,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11762,7 +11765,7 @@
       <c r="F10" s="14" t="n">
         <v>0.05496611353570319</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="13" t="n">
         <v>353.5515330107352</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -11770,7 +11773,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11797,7 +11800,7 @@
       <c r="F11" s="14" t="n">
         <v>0.04339991143104965</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="13" t="n">
         <v>328.4886005113658</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -11805,7 +11808,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11832,7 +11835,7 @@
       <c r="F12" s="14" t="n">
         <v>0.03157810251284246</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="13" t="n">
         <v>1082.840124991685</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -11840,7 +11843,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11867,7 +11870,7 @@
       <c r="F13" s="14" t="n">
         <v>0.02967145546003981</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="13" t="n">
         <v>684.5497593308467</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
@@ -11875,7 +11878,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -11902,7 +11905,7 @@
       <c r="F14" s="14" t="n">
         <v>0.1006985326445986</v>
       </c>
-      <c r="G14" s="15" t="n">
+      <c r="G14" s="13" t="n">
         <v>416.5810486194391</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -11910,7 +11913,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11937,7 +11940,7 @@
       <c r="F15" s="14" t="n">
         <v>0.09124669396316673</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="13" t="n">
         <v>290.6044177775988</v>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -11945,7 +11948,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -11972,7 +11975,7 @@
       <c r="F16" s="14" t="n">
         <v>0.1046183303995765</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="13" t="n">
         <v>232.3254515820871</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -11980,7 +11983,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12007,7 +12010,7 @@
       <c r="F17" s="14" t="n">
         <v>0.09710787736544102</v>
       </c>
-      <c r="G17" s="15" t="n">
+      <c r="G17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -12015,7 +12018,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12042,7 +12045,7 @@
       <c r="F18" s="14" t="n">
         <v>0.04139936350377927</v>
       </c>
-      <c r="G18" s="15" t="n">
+      <c r="G18" s="13" t="n">
         <v>722.8037427593172</v>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -12050,7 +12053,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12077,7 +12080,7 @@
       <c r="F19" s="14" t="n">
         <v>0.05882848525589231</v>
       </c>
-      <c r="G19" s="15" t="n">
+      <c r="G19" s="13" t="n">
         <v>1430.518516283714</v>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -12085,7 +12088,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12112,7 +12115,7 @@
       <c r="F20" s="14" t="n">
         <v>0.02222237749988886</v>
       </c>
-      <c r="G20" s="15" t="n">
+      <c r="G20" s="13" t="n">
         <v>1036.222359581037</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -12120,7 +12123,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12147,7 +12150,7 @@
       <c r="F21" s="14" t="n">
         <v>0.005673803146218766</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="13" t="n">
         <v>485.7051053710738</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
@@ -12155,7 +12158,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12182,7 +12185,7 @@
       <c r="F22" s="14" t="n">
         <v>0.03388654567865802</v>
       </c>
-      <c r="G22" s="15" t="n">
+      <c r="G22" s="13" t="n">
         <v>508.443849607968</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -12190,7 +12193,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12217,7 +12220,7 @@
       <c r="F23" s="14" t="n">
         <v>0.0465354815761925</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="13" t="n">
         <v>1126.87581844462</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
@@ -12225,7 +12228,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12252,7 +12255,7 @@
       <c r="F24" s="14" t="n">
         <v>0.04764929374263268</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="13" t="n">
         <v>1859.688393836288</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -12260,7 +12263,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12287,7 +12290,7 @@
       <c r="F25" s="14" t="n">
         <v>0.08218283422519272</v>
       </c>
-      <c r="G25" s="15" t="n">
+      <c r="G25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -12295,7 +12298,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12322,7 +12325,7 @@
       <c r="F26" s="14" t="n">
         <v>0.03833286712356986</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="13" t="n">
         <v>674.7292879923123</v>
       </c>
       <c r="H26" s="9" t="inlineStr">
@@ -12330,7 +12333,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12357,7 +12360,7 @@
       <c r="F27" s="14" t="n">
         <v>0.02017518356081453</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="13" t="n">
         <v>185.0152992413786</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
@@ -12365,7 +12368,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12392,7 +12395,7 @@
       <c r="F28" s="14" t="n">
         <v>0.0179598792541013</v>
       </c>
-      <c r="G28" s="15" t="n">
+      <c r="G28" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
@@ -12400,7 +12403,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12427,7 +12430,7 @@
       <c r="F29" s="14" t="n">
         <v>0.07322736761869604</v>
       </c>
-      <c r="G29" s="15" t="n">
+      <c r="G29" s="13" t="n">
         <v>1607.862338996289</v>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -12435,7 +12438,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12462,7 +12465,7 @@
       <c r="F30" s="14" t="n">
         <v>0.01599376311311822</v>
       </c>
-      <c r="G30" s="15" t="n">
+      <c r="G30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
@@ -12470,7 +12473,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12497,7 +12500,7 @@
       <c r="F31" s="14" t="n">
         <v>0.109281385074299</v>
       </c>
-      <c r="G31" s="15" t="n">
+      <c r="G31" s="13" t="n">
         <v>120.2955082663782</v>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -12505,7 +12508,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12532,7 +12535,7 @@
       <c r="F32" s="14" t="n">
         <v>0.03586270115751092</v>
       </c>
-      <c r="G32" s="15" t="n">
+      <c r="G32" s="13" t="n">
         <v>7.078359645859189</v>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -12540,7 +12543,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12567,7 +12570,7 @@
       <c r="F33" s="14" t="n">
         <v>0.0555325721079887</v>
       </c>
-      <c r="G33" s="15" t="n">
+      <c r="G33" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -12575,7 +12578,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12602,7 +12605,7 @@
       <c r="F34" s="14" t="n">
         <v>0.03425885056546348</v>
       </c>
-      <c r="G34" s="15" t="n">
+      <c r="G34" s="13" t="n">
         <v>1188.928820354555</v>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -12610,7 +12613,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12637,7 +12640,7 @@
       <c r="F35" s="14" t="n">
         <v>0.04161245433630902</v>
       </c>
-      <c r="G35" s="15" t="n">
+      <c r="G35" s="13" t="n">
         <v>1097.881729794939</v>
       </c>
       <c r="H35" s="9" t="inlineStr">
@@ -12645,7 +12648,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -12672,7 +12675,7 @@
       <c r="F36" s="14" t="n">
         <v>0.04041039859664893</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="13" t="n">
         <v>1549.846588993771</v>
       </c>
       <c r="H36" s="9" t="inlineStr">
@@ -12680,7 +12683,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12707,7 +12710,7 @@
       <c r="F37" s="14" t="n">
         <v>0.1314660180525112</v>
       </c>
-      <c r="G37" s="15" t="n">
+      <c r="G37" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -12715,7 +12718,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12742,7 +12745,7 @@
       <c r="F38" s="14" t="n">
         <v>0.05164645165661454</v>
       </c>
-      <c r="G38" s="15" t="n">
+      <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -12750,7 +12753,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12777,7 +12780,7 @@
       <c r="F39" s="14" t="n">
         <v>0.0216050584167849</v>
       </c>
-      <c r="G39" s="15" t="n">
+      <c r="G39" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="10" t="inlineStr">
@@ -12785,7 +12788,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12812,7 +12815,7 @@
       <c r="F40" s="14" t="n">
         <v>0.01208053615969893</v>
       </c>
-      <c r="G40" s="15" t="n">
+      <c r="G40" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -12820,7 +12823,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12847,7 +12850,7 @@
       <c r="F41" s="14" t="n">
         <v>0.1561309614647208</v>
       </c>
-      <c r="G41" s="15" t="n">
+      <c r="G41" s="13" t="n">
         <v>27.69540057038841</v>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -12855,7 +12858,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -12882,7 +12885,7 @@
       <c r="F42" s="14" t="n">
         <v>0.02681565084272614</v>
       </c>
-      <c r="G42" s="15" t="n">
+      <c r="G42" s="13" t="n">
         <v>1695.943207912471</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
@@ -12890,7 +12893,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12917,7 +12920,7 @@
       <c r="F43" s="14" t="n">
         <v>0.2116472978899012</v>
       </c>
-      <c r="G43" s="15" t="n">
+      <c r="G43" s="13" t="n">
         <v>280.7058518703687</v>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -12925,7 +12928,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -12952,7 +12955,7 @@
       <c r="F44" s="14" t="n">
         <v>0.01648131612753051</v>
       </c>
-      <c r="G44" s="15" t="n">
+      <c r="G44" s="13" t="n">
         <v>1942.344959118177</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
@@ -12960,7 +12963,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -12987,7 +12990,7 @@
       <c r="F45" s="14" t="n">
         <v>0.01464873986283351</v>
       </c>
-      <c r="G45" s="15" t="n">
+      <c r="G45" s="13" t="n">
         <v>977.0400228155836</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
@@ -12995,7 +12998,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13022,7 +13025,7 @@
       <c r="F46" s="14" t="n">
         <v>0.008358631762716987</v>
       </c>
-      <c r="G46" s="15" t="n">
+      <c r="G46" s="13" t="n">
         <v>267.1622968364861</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
@@ -13030,7 +13033,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13057,7 +13060,7 @@
       <c r="F47" s="14" t="n">
         <v>0.04637717121588089</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G47" s="13" t="n">
         <v>2259.839340539176</v>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -13065,7 +13068,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13092,7 +13095,7 @@
       <c r="F48" s="14" t="n">
         <v>0.07756670191185502</v>
       </c>
-      <c r="G48" s="15" t="n">
+      <c r="G48" s="13" t="n">
         <v>455.7515732826328</v>
       </c>
       <c r="H48" s="8" t="inlineStr">
@@ -13100,7 +13103,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13127,7 +13130,7 @@
       <c r="F49" s="14" t="n">
         <v>0.00851107880731611</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G49" s="13" t="n">
         <v>5117.453375841525</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
@@ -13135,7 +13138,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13162,7 +13165,7 @@
       <c r="F50" s="14" t="n">
         <v>0.07841281352823359</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G50" s="13" t="n">
         <v>193.8875566680989</v>
       </c>
       <c r="H50" s="8" t="inlineStr">
@@ -13170,7 +13173,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13197,7 +13200,7 @@
       <c r="F51" s="14" t="n">
         <v>0.003752006354955656</v>
       </c>
-      <c r="G51" s="15" t="n">
+      <c r="G51" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
@@ -13205,7 +13208,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13232,7 +13235,7 @@
       <c r="F52" s="14" t="n">
         <v>0.002265833245462816</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G52" s="13" t="n">
         <v>7454.427897540525</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
@@ -13240,7 +13243,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13267,7 +13270,7 @@
       <c r="F53" s="14" t="n">
         <v>0.03576881060709351</v>
       </c>
-      <c r="G53" s="15" t="n">
+      <c r="G53" s="13" t="n">
         <v>538.038657247266</v>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -13275,7 +13278,7 @@
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13302,7 +13305,7 @@
       <c r="F54" s="14" t="n">
         <v>0.01621975088569496</v>
       </c>
-      <c r="G54" s="15" t="n">
+      <c r="G54" s="13" t="n">
         <v>1729.942536200402</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
@@ -13310,7 +13313,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13337,7 +13340,7 @@
       <c r="F55" s="14" t="n">
         <v>0.02579605574105414</v>
       </c>
-      <c r="G55" s="15" t="n">
+      <c r="G55" s="13" t="n">
         <v>287.8912622543414</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
@@ -13345,7 +13348,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13372,7 +13375,7 @@
       <c r="F56" s="14" t="n">
         <v>0.001034328779856561</v>
       </c>
-      <c r="G56" s="15" t="n">
+      <c r="G56" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
@@ -13380,7 +13383,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13407,7 +13410,7 @@
       <c r="F57" s="14" t="n">
         <v>0.0210718362284322</v>
       </c>
-      <c r="G57" s="15" t="n">
+      <c r="G57" s="13" t="n">
         <v>176.358819279043</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
@@ -13415,7 +13418,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13442,7 +13445,7 @@
       <c r="F58" s="14" t="n">
         <v>0.01618867833507467</v>
       </c>
-      <c r="G58" s="15" t="n">
+      <c r="G58" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
@@ -13450,7 +13453,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13477,7 +13480,7 @@
       <c r="F59" s="14" t="n">
         <v>0.01692324119915931</v>
       </c>
-      <c r="G59" s="15" t="n">
+      <c r="G59" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="10" t="inlineStr">
@@ -13485,7 +13488,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13512,7 +13515,7 @@
       <c r="F60" s="14" t="n">
         <v>0.02093916975195698</v>
       </c>
-      <c r="G60" s="15" t="n">
+      <c r="G60" s="13" t="n">
         <v>3652.406396220297</v>
       </c>
       <c r="H60" s="10" t="inlineStr">
@@ -13520,7 +13523,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13547,7 +13550,7 @@
       <c r="F61" s="14" t="n">
         <v>0.002568037786274691</v>
       </c>
-      <c r="G61" s="15" t="n">
+      <c r="G61" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="10" t="inlineStr">
@@ -13555,7 +13558,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13582,7 +13585,7 @@
       <c r="F62" s="14" t="n">
         <v>0.01190660577316193</v>
       </c>
-      <c r="G62" s="15" t="n">
+      <c r="G62" s="13" t="n">
         <v>899.4908331833321</v>
       </c>
       <c r="H62" s="10" t="inlineStr">
@@ -13590,7 +13593,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I62" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -13617,7 +13620,7 @@
       <c r="F63" s="14" t="n">
         <v>0.0004562102698957172</v>
       </c>
-      <c r="G63" s="15" t="n">
+      <c r="G63" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="10" t="inlineStr">
@@ -13625,7 +13628,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13652,7 +13655,7 @@
       <c r="F64" s="14" t="n">
         <v>0.0003292579801545917</v>
       </c>
-      <c r="G64" s="15" t="n">
+      <c r="G64" s="13" t="n">
         <v>3081.637122894453</v>
       </c>
       <c r="H64" s="10" t="inlineStr">
@@ -13660,7 +13663,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -13687,7 +13690,7 @@
       <c r="F65" s="14" t="n">
         <v>0.0003652867500988276</v>
       </c>
-      <c r="G65" s="15" t="n">
+      <c r="G65" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="10" t="inlineStr">
@@ -13695,7 +13698,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13722,7 +13725,7 @@
       <c r="F66" s="14" t="n">
         <v>0.01677354764575148</v>
       </c>
-      <c r="G66" s="15" t="n">
+      <c r="G66" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
@@ -13730,7 +13733,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13757,7 +13760,7 @@
       <c r="F67" s="14" t="n">
         <v>0.01069276385820937</v>
       </c>
-      <c r="G67" s="15" t="n">
+      <c r="G67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
@@ -13765,7 +13768,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13792,7 +13795,7 @@
       <c r="F68" s="14" t="n">
         <v>0.009827141572382358</v>
       </c>
-      <c r="G68" s="15" t="n">
+      <c r="G68" s="13" t="n">
         <v>519.250278435678</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
@@ -13800,7 +13803,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -13827,7 +13830,7 @@
       <c r="F69" s="14" t="n">
         <v>0.05829550100049487</v>
       </c>
-      <c r="G69" s="15" t="n">
+      <c r="G69" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="8" t="inlineStr">
@@ -13835,7 +13838,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13862,7 +13865,7 @@
       <c r="F70" s="14" t="n">
         <v>0.351648446391006</v>
       </c>
-      <c r="G70" s="15" t="n">
+      <c r="G70" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="7" t="inlineStr">
@@ -13870,7 +13873,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13897,7 +13900,7 @@
       <c r="F71" s="14" t="n">
         <v>0.3603993833051905</v>
       </c>
-      <c r="G71" s="15" t="n">
+      <c r="G71" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="7" t="inlineStr">
@@ -13905,7 +13908,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13932,7 +13935,7 @@
       <c r="F72" s="14" t="n">
         <v>0.2342780039109946</v>
       </c>
-      <c r="G72" s="15" t="n">
+      <c r="G72" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="7" t="inlineStr">
@@ -13940,7 +13943,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -13967,7 +13970,7 @@
       <c r="F73" s="14" t="n">
         <v>0.006449319769579605</v>
       </c>
-      <c r="G73" s="15" t="n">
+      <c r="G73" s="13" t="n">
         <v>570.8542713567839</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
@@ -13975,7 +13978,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I73" s="5" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -14002,7 +14005,7 @@
       <c r="F74" s="14" t="n">
         <v>0.02001112591691787</v>
       </c>
-      <c r="G74" s="15" t="n">
+      <c r="G74" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
@@ -14010,7 +14013,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14037,7 +14040,7 @@
       <c r="F75" s="14" t="n">
         <v>0.02403209618177159</v>
       </c>
-      <c r="G75" s="15" t="n">
+      <c r="G75" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
@@ -14045,7 +14048,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14072,7 +14075,7 @@
       <c r="F76" s="14" t="n">
         <v>0.00710859860222045</v>
       </c>
-      <c r="G76" s="15" t="n">
+      <c r="G76" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
@@ -14080,7 +14083,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14107,7 +14110,7 @@
       <c r="F77" s="14" t="n">
         <v>0.02896928037416292</v>
       </c>
-      <c r="G77" s="15" t="n">
+      <c r="G77" s="13" t="n">
         <v>4382.702051518266</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
@@ -14115,7 +14118,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I77" s="5" t="inlineStr">
+      <c r="I77" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -14142,7 +14145,7 @@
       <c r="F78" s="14" t="n">
         <v>0.001087899429741606</v>
       </c>
-      <c r="G78" s="15" t="n">
+      <c r="G78" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
@@ -14150,7 +14153,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14177,7 +14180,7 @@
       <c r="F79" s="14" t="n">
         <v>0.05379357436003215</v>
       </c>
-      <c r="G79" s="15" t="n">
+      <c r="G79" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="8" t="inlineStr">
@@ -14185,7 +14188,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14212,7 +14215,7 @@
       <c r="F80" s="14" t="n">
         <v>0.02454440944424385</v>
       </c>
-      <c r="G80" s="15" t="n">
+      <c r="G80" s="13" t="n">
         <v>2492.249461508772</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
@@ -14220,7 +14223,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -14247,7 +14250,7 @@
       <c r="F81" s="14" t="n">
         <v>0.00243985058776138</v>
       </c>
-      <c r="G81" s="15" t="n">
+      <c r="G81" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
@@ -14255,7 +14258,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14282,7 +14285,7 @@
       <c r="F82" s="14" t="n">
         <v>0.005863445631130913</v>
       </c>
-      <c r="G82" s="15" t="n">
+      <c r="G82" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
@@ -14290,7 +14293,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14317,7 +14320,7 @@
       <c r="F83" s="14" t="n">
         <v>0.1657077154120518</v>
       </c>
-      <c r="G83" s="15" t="n">
+      <c r="G83" s="13" t="n">
         <v>1656.654777548339</v>
       </c>
       <c r="H83" s="8" t="inlineStr">
@@ -14325,7 +14328,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I83" s="5" t="inlineStr">
+      <c r="I83" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -14352,7 +14355,7 @@
       <c r="F84" s="14" t="n">
         <v>0.012870024978009</v>
       </c>
-      <c r="G84" s="15" t="n">
+      <c r="G84" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="10" t="inlineStr">
@@ -14360,7 +14363,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I84" s="5" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14387,7 +14390,7 @@
       <c r="F85" s="14" t="n">
         <v>0.02999733507764614</v>
       </c>
-      <c r="G85" s="15" t="n">
+      <c r="G85" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="10" t="inlineStr">
@@ -14395,7 +14398,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14422,7 +14425,7 @@
       <c r="F86" s="14" t="n">
         <v>0.2690340302447926</v>
       </c>
-      <c r="G86" s="15" t="n">
+      <c r="G86" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="7" t="inlineStr">
@@ -14430,7 +14433,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I86" s="5" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14457,7 +14460,7 @@
       <c r="F87" s="14" t="n">
         <v>0.02640247224074819</v>
       </c>
-      <c r="G87" s="15" t="n">
+      <c r="G87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="10" t="inlineStr">
@@ -14465,7 +14468,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I87" s="5" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14492,7 +14495,7 @@
       <c r="F88" s="14" t="n">
         <v>0.1795065291325253</v>
       </c>
-      <c r="G88" s="15" t="n">
+      <c r="G88" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="8" t="inlineStr">
@@ -14500,7 +14503,7 @@
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14527,7 +14530,7 @@
       <c r="F89" s="14" t="n">
         <v>0.009011163003225103</v>
       </c>
-      <c r="G89" s="15" t="n">
+      <c r="G89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="10" t="inlineStr">
@@ -14535,7 +14538,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I89" s="5" t="inlineStr">
+      <c r="I89" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14562,7 +14565,7 @@
       <c r="F90" s="14" t="n">
         <v>0.004447938773490505</v>
       </c>
-      <c r="G90" s="15" t="n">
+      <c r="G90" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
@@ -14570,7 +14573,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I90" s="5" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14597,7 +14600,7 @@
       <c r="F91" s="14" t="n">
         <v>0.2621025239831106</v>
       </c>
-      <c r="G91" s="15" t="n">
+      <c r="G91" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="7" t="inlineStr">
@@ -14605,7 +14608,7 @@
           <t>Crítica</t>
         </is>
       </c>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -14632,7 +14635,7 @@
       <c r="F92" s="14" t="n">
         <v>0.006408800890079698</v>
       </c>
-      <c r="G92" s="15" t="n">
+      <c r="G92" s="13" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
@@ -14640,7 +14643,7 @@
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>

--- a/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
+++ b/rates-nodispo/week-19/Analisis_Rates_NoDispo_OP_7d.xlsx
@@ -547,7 +547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3469,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7867,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -9710,7 +9710,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
